--- a/Timesheet-Project/Timesheet 3/Lwazisile/Lwazisile_Mhlambi_April_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Lwazisile/Lwazisile_Mhlambi_April_FinalWeek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://northerndata-my.sharepoint.com/personal/lwazisile_mhlambi_sambeconsulting_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Lwazisile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="732" documentId="13_ncr:1_{18456319-F974-4A60-AFC5-4E049C41B553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CA1AEDF-48AE-47CD-8FFA-D0F2AA27F5C0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE14221B-A312-4EAE-8F76-E53953F77108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="3204" yWindow="3204" windowWidth="17280" windowHeight="8880" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Apr" sheetId="10" r:id="rId1"/>
@@ -776,7 +776,7 @@
     <numFmt numFmtId="166" formatCode="_ [$R-1C09]\ * #,##0.00_ ;_ [$R-1C09]\ * \-#,##0.00_ ;_ [$R-1C09]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="[$R-1C09]#,##0.00;\-[$R-1C09]#,##0.00"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1859,13 +1859,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1881,21 +1896,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1954,147 +1954,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="103">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2767,6 +2626,147 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6758C6CA-2356-4535-9D9D-86230C423211}"/>
@@ -3175,26 +3175,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H76" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H76" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101">
   <autoFilter ref="H2:H76" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:H76">
     <sortCondition ref="H64:H76"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{234A6588-4DEA-4067-9367-AEAFE02CA40D}" name="Resource" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}" name="ProjectTable" displayName="ProjectTable" ref="F2:F40" totalsRowShown="0" headerRowDxfId="99" dataDxfId="98" tableBorderDxfId="97">
   <autoFilter ref="F2:F40" xr:uid="{B149CFBE-03DA-4A5C-8F86-52A53133C863}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F3:F19">
     <sortCondition ref="F2:F19"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D9788319-59C4-447A-9364-6F4EF6730453}" name="Description" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3470,19 +3470,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B63D3D5-6C83-45F2-B2A7-43EE15BF1EF3}">
-  <dimension ref="A5:J179"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <dimension ref="A5:J169"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -3503,7 +3503,7 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="37"/>
       <c r="B7" s="46"/>
       <c r="C7" s="37"/>
@@ -3512,7 +3512,7 @@
       <c r="H7" s="40"/>
       <c r="J7" s="41"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="12.75">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46113</v>
       </c>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>16</v>
@@ -3575,7 +3575,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="12.75">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46113</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>0.34513888888888888</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12.75">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46113</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>0.40277777777777779</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="12.75">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46113</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>0.42569444444444443</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="12.75">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46113</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="12.75">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46113</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>0.48125000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="12.75">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46113</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>0.51180555555555551</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="12.75">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46113</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>0.52847222222222223</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="12.75">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46113</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="12.75">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46113</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>0.74583333333333335</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="12.75">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46114</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="12.75">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46114</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>0.33750000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="12.75">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46114</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="12.75">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46114</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>0.49444444444444446</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="12.75">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46114</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>0.5395833333333333</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="12.75">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46114</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="12.75">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46114</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>0.72638888888888886</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="47">
         <v>46115</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>29</v>
       </c>
       <c r="H26" s="50">
-        <f t="shared" ref="H26:H137" si="2">J26-I26</f>
+        <f t="shared" ref="H26:H135" si="2">J26-I26</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="I26" s="51">
@@ -4102,7 +4102,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>46116</v>
       </c>
@@ -4121,7 +4121,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>46117</v>
       </c>
@@ -4140,7 +4140,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="47">
         <v>46118</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="12.75">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46119</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="12.75">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46119</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="12.75">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46119</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>0.48541666666666666</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="12.75">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46119</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>0.5395833333333333</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="12.75">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46119</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="12.75">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46119</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>0.72638888888888886</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="12.75">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46120</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="12.75">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46120</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>0.34097222222222223</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="12.75">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46120</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="12.75">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>46120</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>0.4909722222222222</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="12.75">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="22">
         <v>46120</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>0.52152777777777781</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="12.75">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="22">
         <v>46120</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="12.75">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="22">
         <v>46120</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>0.68888888888888888</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="12.75">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="22">
         <v>46120</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>0.7319444444444444</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="12.75">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="22">
         <v>46121</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>0.3298611111111111</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="12.75">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="22">
         <v>46121</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>0.33402777777777776</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="12.75">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="22">
         <v>46121</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="12.75">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="22">
         <v>46121</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>0.49513888888888891</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="12.75">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="22">
         <v>46121</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>0.52708333333333335</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="12.75">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="22">
         <v>46121</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="12.75">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="22">
         <v>46121</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="12.75">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="22">
         <v>46121</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="12.75">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="22">
         <v>46121</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>0.33819444444444446</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="12.75">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="22">
         <v>46121</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="12.75">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="22">
         <v>46121</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>0.49166666666666664</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="12.75">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="22">
         <v>46121</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="12.75">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="31">
         <v>46123</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="I56" s="35"/>
       <c r="J56" s="35"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="31">
         <v>46124</v>
       </c>
@@ -5015,7 +5015,7 @@
       <c r="I57" s="35"/>
       <c r="J57" s="35"/>
     </row>
-    <row r="58" spans="1:10" ht="12.75">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="22">
         <v>46125</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="12.75">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="22">
         <v>46125</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>35</v>
       </c>
       <c r="H59" s="29">
-        <f t="shared" ref="H59:H77" si="8">J59-I59</f>
+        <f t="shared" ref="H59:H71" si="8">J59-I59</f>
         <v>0.125</v>
       </c>
       <c r="I59" s="30">
@@ -5077,7 +5077,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="12.75">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="22">
         <v>46125</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>0.48055555555555557</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="12.75">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="22">
         <v>46125</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>0.53888888888888886</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="12.75">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="22">
         <v>46125</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="12.75">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="22">
         <v>46125</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>0.70972222222222225</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="12.75">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="22">
         <v>46126</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="12.75">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="22">
         <v>46126</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>0.33888888888888891</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="12.75">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
         <v>46126</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="12.75">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="22">
         <v>46126</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>0.49652777777777779</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="12.75">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
         <v>46126</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>0.53680555555555554</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="12.75">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
         <v>46126</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="12.75">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
         <v>46126</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="12.75">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
         <v>46127</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="12.75">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
         <v>46127</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>19</v>
       </c>
       <c r="H72" s="29">
-        <f t="shared" ref="H72:H91" si="10">J72-I72</f>
+        <f t="shared" ref="H72:H84" si="10">J72-I72</f>
         <v>2.7777777777778234E-3</v>
       </c>
       <c r="I72" s="30">
@@ -5480,7 +5480,7 @@
         <v>0.33611111111111114</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="12.75">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="22">
         <v>46127</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="12.75">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="22">
         <v>46127</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>0.47916666666666669</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="12.75">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="22">
         <v>46127</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>0.54097222222222219</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="12.75">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="22">
         <v>46127</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="12.75">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="22">
         <v>46127</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="12.75">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="22">
         <v>46128</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>0.33819444444444446</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="12.75">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="22">
         <v>46128</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="12.75">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="22">
         <v>46128</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>0.48472222222222222</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="12.75">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="22">
         <v>46128</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>0.54097222222222219</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="12.75">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="22">
         <v>46128</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="12.75">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="22">
         <v>46128</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>0.73472222222222228</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="12.75">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="22">
         <v>46129</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="12.75">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="22">
         <v>46129</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>0.36180555555555555</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="12.75">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="22">
         <v>46129</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="12.75">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="22">
         <v>46129</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="12.75">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="22">
         <v>46129</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>0.54097222222222219</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="12.75">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="22">
         <v>46129</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="12.75">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="22">
         <v>46129</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="12.75">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="22">
         <v>46129</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="31">
         <v>46130</v>
       </c>
@@ -6088,7 +6088,7 @@
       <c r="I92" s="35"/>
       <c r="J92" s="35"/>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="31">
         <v>46131</v>
       </c>
@@ -6107,7 +6107,7 @@
       <c r="I93" s="35"/>
       <c r="J93" s="35"/>
     </row>
-    <row r="94" spans="1:10" ht="12.75">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="22">
         <v>46132</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>0.33680555555555558</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="12.75">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="22">
         <v>46132</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>0.34652777777777777</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="25.5">
+    <row r="96" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A96" s="22">
         <v>46132</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>0.45208333333333334</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="12.75">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="22">
         <v>46132</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="12.75">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="22">
         <v>46132</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>0.53472222222222221</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="12.75">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="22">
         <v>46132</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="12.75">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="22">
         <v>46132</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>0.69444444444444442</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="12.75">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="22">
         <v>46132</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>0.71944444444444444</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="12.75">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="22">
         <v>46133</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="12.75">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="22">
         <v>46133</v>
       </c>
@@ -6417,7 +6417,7 @@
         <v>0.33541666666666664</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="12.75">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="22">
         <v>46133</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="12.75">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="22">
         <v>46133</v>
       </c>
@@ -6479,7 +6479,7 @@
         <v>0.49791666666666667</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="12.75">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="22">
         <v>46133</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>0.5395833333333333</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="12.75">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="22">
         <v>46133</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="12.75">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="22">
         <v>46133</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>0.7104166666666667</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="12.75">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="22">
         <v>46134</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="12.75">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="22">
         <v>46134</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>0.33958333333333335</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="12.75">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="22">
         <v>46134</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="12.75">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="22">
         <v>46134</v>
       </c>
@@ -6696,7 +6696,7 @@
         <v>0.51041666666666663</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="12.75">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="22">
         <v>46134</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>0.54097222222222219</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="12.75">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="22">
         <v>46134</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="12.75">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="22">
         <v>46134</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>0.71597222222222223</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="12.75">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="22">
         <v>46135</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="12.75">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="22">
         <v>46135</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>0.33611111111111114</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="12.75">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="22">
         <v>46135</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="12.75">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="22">
         <v>46135</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>0.50763888888888886</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="12.75">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="22">
         <v>46135</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>0.54097222222222219</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="12.75">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="22">
         <v>46135</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="12.75">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="22">
         <v>46135</v>
       </c>
@@ -7006,7 +7006,7 @@
         <v>0.70902777777777781</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="12.75">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="22">
         <v>46136</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>0.3298611111111111</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="12.75">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="22">
         <v>46136</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>0.34236111111111112</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="12.75">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="22">
         <v>46136</v>
       </c>
@@ -7099,7 +7099,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="12.75">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="22">
         <v>46136</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>0.49305555555555558</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="12.75">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="22">
         <v>46136</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>0.53749999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="12.75">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="22">
         <v>46136</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="12.75">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="22">
         <v>46136</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>0.61527777777777781</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="12.75">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="22">
         <v>46136</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="12.75">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="22">
         <v>46136</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="31">
         <v>46137</v>
       </c>
@@ -7304,7 +7304,7 @@
       <c r="I132" s="35"/>
       <c r="J132" s="35"/>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="31">
         <v>46138</v>
       </c>
@@ -7323,7 +7323,7 @@
       <c r="I133" s="35"/>
       <c r="J133" s="35"/>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="47">
         <v>46139</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="12.75">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="22">
         <v>46140</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>0.33750000000000002</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="12.75">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="22">
         <v>46140</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>35</v>
       </c>
       <c r="H136" s="29">
-        <f t="shared" ref="H136:H145" si="18">J136-I136</f>
+        <f t="shared" ref="H136:H144" si="18">J136-I136</f>
         <v>0.12083333333333329</v>
       </c>
       <c r="I136" s="30">
@@ -7416,7 +7416,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="12.75">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="22">
         <v>46140</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>0.50138888888888888</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="12.75">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="22">
         <v>46140</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>0.53888888888888886</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="12.75">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="22">
         <v>46140</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>0.60277777777777775</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="12.75">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="22">
         <v>46140</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>0.64722222222222225</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="12.75">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="22">
         <v>46140</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="12.75">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="22">
         <v>46140</v>
       </c>
@@ -7602,7 +7602,7 @@
         <v>0.70208333333333328</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="12.75">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="22">
         <v>46140</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>0.71111111111111114</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="12.75">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="22">
         <v>46141</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>0.34652777777777777</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="12.75">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="22">
         <v>46141</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>0.39583333333333331</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="12.75">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="22">
         <v>46141</v>
       </c>
@@ -7726,7 +7726,7 @@
         <v>0.45347222222222222</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="12.75">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="22">
         <v>46141</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>0.49236111111111114</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="12.75">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="22">
         <v>46141</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>0.54027777777777775</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="12.75">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="22">
         <v>46141</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="12.75">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="22">
         <v>46141</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>0.71250000000000002</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="12.75">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="22">
         <v>46142</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>0.34861111111111109</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="12.75">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="22">
         <v>46142</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="12.75">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="22">
         <v>46142</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>0.45902777777777776</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="12.75">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="22">
         <v>46142</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="12.75">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="22">
         <v>46142</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>0.54236111111111107</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="12.75">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="22">
         <v>46142</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="12.75">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="22">
         <v>46142</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="12.75">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="22">
         <v>46142</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>0.71597222222222223</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="12.75">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="22">
         <v>46142</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="160" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A160" s="46"/>
       <c r="B160" s="46"/>
       <c r="G160" s="40"/>
@@ -8137,7 +8137,7 @@
       <c r="I160" s="65"/>
       <c r="J160" s="65"/>
     </row>
-    <row r="161" spans="1:8" ht="13.9" customHeight="1">
+    <row r="161" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="5"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="H161" s="40"/>
     </row>
-    <row r="162" spans="1:8" ht="13.9" customHeight="1" thickBot="1">
+    <row r="162" spans="1:8" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="9"/>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="H162" s="40"/>
     </row>
-    <row r="163" spans="1:8" ht="13.9" customHeight="1" thickBot="1">
+    <row r="163" spans="1:8" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="122" t="s">
         <v>55</v>
       </c>
@@ -8174,7 +8174,7 @@
       <c r="F163" s="2"/>
       <c r="H163" s="40"/>
     </row>
-    <row r="164" spans="1:8" ht="13.9">
+    <row r="164" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A164" s="13"/>
       <c r="B164" s="13"/>
       <c r="C164" s="6"/>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H164" s="38"/>
     </row>
-    <row r="165" spans="1:8" ht="15" customHeight="1" thickBot="1">
+    <row r="165" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="123" t="s">
         <v>57</v>
       </c>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="H165" s="40"/>
     </row>
-    <row r="166" spans="1:8" ht="14.45" thickBot="1">
+    <row r="166" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H166" s="40"/>
     </row>
-    <row r="167" spans="1:8" ht="13.9" thickBot="1">
+    <row r="167" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -8227,7 +8227,7 @@
       <c r="F167" s="2"/>
       <c r="H167" s="40"/>
     </row>
-    <row r="168" spans="1:8" ht="13.9" thickBot="1">
+    <row r="168" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -8238,20 +8238,10 @@
       <c r="F168" s="21"/>
       <c r="H168" s="40"/>
     </row>
-    <row r="169" spans="1:8" ht="13.15" thickBot="1">
+    <row r="169" spans="1:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E169" s="39"/>
       <c r="H169" s="40"/>
     </row>
-    <row r="170" spans="1:8" ht="12.75"/>
-    <row r="171" spans="1:8" ht="12.75"/>
-    <row r="172" spans="1:8" ht="12.75"/>
-    <row r="173" spans="1:8" ht="12.75"/>
-    <row r="174" spans="1:8" ht="12.75"/>
-    <row r="175" spans="1:8" ht="12.75"/>
-    <row r="176" spans="1:8" ht="12.75"/>
-    <row r="177" ht="12.75"/>
-    <row r="178" ht="12.75"/>
-    <row r="179" ht="12.75"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A163:C163"/>
@@ -8259,56 +8249,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D7:E7">
-    <cfRule type="containsText" dxfId="102" priority="12" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="95" priority="12" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="101" priority="13" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="94" priority="13" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="14" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="93" priority="14" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="15" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="92" priority="15" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="16" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="91" priority="16" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="17" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="90" priority="17" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="18" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B169">
-    <cfRule type="containsText" dxfId="95" priority="1" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="2" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="87" priority="2" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D161:E161 D163:E165 E168">
-    <cfRule type="containsText" dxfId="93" priority="3" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="86" priority="3" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D161)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="4" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="85" priority="4" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D161)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="5" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="84" priority="5" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D161)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="6" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="83" priority="6" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D161)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="7" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="82" priority="7" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D161)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="8" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="81" priority="8" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D161)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="9" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8357,18 +8347,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE93A-CBFB-4D27-9D4A-1E2332DAE6F0}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -8378,7 +8368,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -8392,10 +8382,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -8427,7 +8417,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="47">
         <v>46143</v>
       </c>
@@ -8458,7 +8448,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
         <v>46144</v>
       </c>
@@ -8477,7 +8467,7 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
         <v>46145</v>
       </c>
@@ -8496,7 +8486,7 @@
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46146</v>
       </c>
@@ -8529,7 +8519,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46147</v>
       </c>
@@ -8548,7 +8538,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46148</v>
       </c>
@@ -8567,7 +8557,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46149</v>
       </c>
@@ -8586,7 +8576,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46150</v>
       </c>
@@ -8605,7 +8595,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
         <v>46151</v>
       </c>
@@ -8624,7 +8614,7 @@
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="31">
         <v>46152</v>
       </c>
@@ -8643,7 +8633,7 @@
       <c r="I18" s="35"/>
       <c r="J18" s="35"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46153</v>
       </c>
@@ -8662,7 +8652,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46154</v>
       </c>
@@ -8681,7 +8671,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46155</v>
       </c>
@@ -8700,7 +8690,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46156</v>
       </c>
@@ -8719,7 +8709,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46157</v>
       </c>
@@ -8738,7 +8728,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>46158</v>
       </c>
@@ -8757,7 +8747,7 @@
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>46159</v>
       </c>
@@ -8776,7 +8766,7 @@
       <c r="I25" s="35"/>
       <c r="J25" s="35"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46160</v>
       </c>
@@ -8795,7 +8785,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46161</v>
       </c>
@@ -8814,7 +8804,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46162</v>
       </c>
@@ -8833,7 +8823,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46163</v>
       </c>
@@ -8852,7 +8842,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46164</v>
       </c>
@@ -8871,7 +8861,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>46165</v>
       </c>
@@ -8890,7 +8880,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="31">
         <v>46166</v>
       </c>
@@ -8909,7 +8899,7 @@
       <c r="I32" s="35"/>
       <c r="J32" s="35"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46167</v>
       </c>
@@ -8928,7 +8918,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46168</v>
       </c>
@@ -8947,7 +8937,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46169</v>
       </c>
@@ -8966,7 +8956,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46170</v>
       </c>
@@ -8985,7 +8975,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46171</v>
       </c>
@@ -9004,7 +8994,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>46172</v>
       </c>
@@ -9023,7 +9013,7 @@
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31">
         <v>46173</v>
       </c>
@@ -9042,7 +9032,7 @@
       <c r="I39" s="98"/>
       <c r="J39" s="32"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="46"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -9053,7 +9043,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -9066,7 +9056,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -9079,7 +9069,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="122" t="s">
         <v>55</v>
       </c>
@@ -9090,7 +9080,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -9104,7 +9094,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="123" t="s">
         <v>57</v>
       </c>
@@ -9120,7 +9110,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -9134,7 +9124,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -9143,7 +9133,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -9154,7 +9144,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -9165,56 +9155,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="86" priority="21" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="79" priority="21" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="22" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="78" priority="22" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="77" priority="23" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="24" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="76" priority="24" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="25" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="75" priority="25" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="26" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="74" priority="26" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="27" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="79" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="72" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="71" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="77" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="70" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="69" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="68" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="67" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="66" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="65" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9266,18 +9256,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738C92ED-F226-4107-8C14-FCA383B998C3}">
   <dimension ref="A5:J48"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -9287,7 +9277,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -9301,10 +9291,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -9336,7 +9326,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46174</v>
       </c>
@@ -9369,7 +9359,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46175</v>
       </c>
@@ -9388,7 +9378,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46176</v>
       </c>
@@ -9407,7 +9397,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46177</v>
       </c>
@@ -9426,7 +9416,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46178</v>
       </c>
@@ -9445,7 +9435,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>46179</v>
       </c>
@@ -9464,7 +9454,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>46180</v>
       </c>
@@ -9483,7 +9473,7 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46181</v>
       </c>
@@ -9502,7 +9492,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46182</v>
       </c>
@@ -9521,7 +9511,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46183</v>
       </c>
@@ -9540,7 +9530,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46184</v>
       </c>
@@ -9559,7 +9549,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46185</v>
       </c>
@@ -9578,7 +9568,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
         <v>46186</v>
       </c>
@@ -9597,7 +9587,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
         <v>46187</v>
       </c>
@@ -9616,7 +9606,7 @@
       <c r="I22" s="35"/>
       <c r="J22" s="35"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46188</v>
       </c>
@@ -9635,7 +9625,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="47">
         <v>46189</v>
       </c>
@@ -9666,7 +9656,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46190</v>
       </c>
@@ -9685,7 +9675,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46191</v>
       </c>
@@ -9704,7 +9694,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46192</v>
       </c>
@@ -9723,7 +9713,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>46193</v>
       </c>
@@ -9742,7 +9732,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="31">
         <v>46194</v>
       </c>
@@ -9761,7 +9751,7 @@
       <c r="I29" s="35"/>
       <c r="J29" s="35"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46195</v>
       </c>
@@ -9780,7 +9770,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46196</v>
       </c>
@@ -9799,7 +9789,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46197</v>
       </c>
@@ -9818,7 +9808,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46198</v>
       </c>
@@ -9837,7 +9827,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46199</v>
       </c>
@@ -9856,7 +9846,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="31">
         <v>46200</v>
       </c>
@@ -9875,7 +9865,7 @@
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="31">
         <v>46201</v>
       </c>
@@ -9894,7 +9884,7 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46202</v>
       </c>
@@ -9913,7 +9903,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10" ht="13.15" thickBot="1">
+    <row r="38" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22">
         <v>46203</v>
       </c>
@@ -9932,7 +9922,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="45"/>
       <c r="B39" s="45"/>
       <c r="C39" s="45"/>
@@ -9943,7 +9933,7 @@
       <c r="H39" s="36"/>
       <c r="I39" s="37"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -9956,7 +9946,7 @@
       </c>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="9"/>
@@ -9969,7 +9959,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="122" t="s">
         <v>55</v>
       </c>
@@ -9980,7 +9970,7 @@
       <c r="F42" s="2"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9">
+    <row r="43" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
@@ -9994,7 +9984,7 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="123" t="s">
         <v>57</v>
       </c>
@@ -10010,7 +10000,7 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.45" thickBot="1">
+    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -10024,7 +10014,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.9" thickBot="1">
+    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -10033,7 +10023,7 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -10044,7 +10034,7 @@
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.15" thickBot="1">
+    <row r="48" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -10055,56 +10045,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="70" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="63" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="61" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="60" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="59" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="58" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B48">
-    <cfRule type="containsText" dxfId="63" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="56" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="55" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:E40 D42:E44 E47">
-    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="54" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="53" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="52" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="51" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="50" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="49" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D39)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10162,18 +10152,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077AC14-6A48-4DDF-A891-D5BFFE7E5F3C}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -10183,7 +10173,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -10197,10 +10187,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -10232,7 +10222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46204</v>
       </c>
@@ -10265,7 +10255,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46205</v>
       </c>
@@ -10284,7 +10274,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46206</v>
       </c>
@@ -10303,7 +10293,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
         <v>46207</v>
       </c>
@@ -10322,7 +10312,7 @@
       <c r="I12" s="35"/>
       <c r="J12" s="35"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
         <v>46208</v>
       </c>
@@ -10341,7 +10331,7 @@
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46209</v>
       </c>
@@ -10360,7 +10350,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46210</v>
       </c>
@@ -10379,7 +10369,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46211</v>
       </c>
@@ -10398,7 +10388,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46212</v>
       </c>
@@ -10417,7 +10407,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46213</v>
       </c>
@@ -10436,7 +10426,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="31">
         <v>46214</v>
       </c>
@@ -10455,7 +10445,7 @@
       <c r="I19" s="35"/>
       <c r="J19" s="35"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
         <v>46215</v>
       </c>
@@ -10474,7 +10464,7 @@
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46216</v>
       </c>
@@ -10493,7 +10483,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46217</v>
       </c>
@@ -10512,7 +10502,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46218</v>
       </c>
@@ -10531,7 +10521,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46219</v>
       </c>
@@ -10550,7 +10540,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46220</v>
       </c>
@@ -10569,7 +10559,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>46221</v>
       </c>
@@ -10588,7 +10578,7 @@
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>46222</v>
       </c>
@@ -10607,7 +10597,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46223</v>
       </c>
@@ -10626,7 +10616,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46224</v>
       </c>
@@ -10645,7 +10635,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46225</v>
       </c>
@@ -10664,7 +10654,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46226</v>
       </c>
@@ -10683,7 +10673,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46227</v>
       </c>
@@ -10702,7 +10692,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="31">
         <v>46228</v>
       </c>
@@ -10721,7 +10711,7 @@
       <c r="I33" s="35"/>
       <c r="J33" s="35"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="31">
         <v>46229</v>
       </c>
@@ -10740,7 +10730,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46230</v>
       </c>
@@ -10759,7 +10749,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46231</v>
       </c>
@@ -10778,7 +10768,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46232</v>
       </c>
@@ -10797,7 +10787,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46233</v>
       </c>
@@ -10816,7 +10806,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.15" thickBot="1">
+    <row r="39" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22">
         <v>46234</v>
       </c>
@@ -10835,7 +10825,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -10846,7 +10836,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -10859,7 +10849,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -10872,7 +10862,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="122" t="s">
         <v>55</v>
       </c>
@@ -10883,7 +10873,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -10897,7 +10887,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="123" t="s">
         <v>57</v>
       </c>
@@ -10913,7 +10903,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -10927,7 +10917,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -10936,7 +10926,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -10947,7 +10937,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -10958,56 +10948,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="54" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="47" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="46" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="45" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="44" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="43" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="42" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="47" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="37" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="35" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11069,18 +11059,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5FF808-4CDC-4429-9978-CAD26FE6591A}">
   <dimension ref="A5:J49"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -11090,7 +11080,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -11104,10 +11094,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -11139,7 +11129,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
         <v>46235</v>
       </c>
@@ -11158,7 +11148,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
         <v>46236</v>
       </c>
@@ -11177,7 +11167,7 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46237</v>
       </c>
@@ -11210,7 +11200,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46238</v>
       </c>
@@ -11229,7 +11219,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46239</v>
       </c>
@@ -11248,7 +11238,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="22">
         <v>46240</v>
       </c>
@@ -11267,7 +11257,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46241</v>
       </c>
@@ -11286,7 +11276,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
         <v>46242</v>
       </c>
@@ -11305,7 +11295,7 @@
       <c r="I16" s="35"/>
       <c r="J16" s="35"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
         <v>46243</v>
       </c>
@@ -11326,7 +11316,7 @@
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="47">
         <v>46244</v>
       </c>
@@ -11357,7 +11347,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46245</v>
       </c>
@@ -11376,7 +11366,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="22">
         <v>46246</v>
       </c>
@@ -11395,7 +11385,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="22">
         <v>46247</v>
       </c>
@@ -11414,7 +11404,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46248</v>
       </c>
@@ -11433,7 +11423,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="31">
         <v>46249</v>
       </c>
@@ -11452,7 +11442,7 @@
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>46250</v>
       </c>
@@ -11471,7 +11461,7 @@
       <c r="I24" s="35"/>
       <c r="J24" s="35"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46251</v>
       </c>
@@ -11490,7 +11480,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46252</v>
       </c>
@@ -11509,7 +11499,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46253</v>
       </c>
@@ -11528,7 +11518,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46254</v>
       </c>
@@ -11547,7 +11537,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46255</v>
       </c>
@@ -11566,7 +11556,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="31">
         <v>46256</v>
       </c>
@@ -11585,7 +11575,7 @@
       <c r="I30" s="35"/>
       <c r="J30" s="35"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>46257</v>
       </c>
@@ -11604,7 +11594,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="22">
         <v>46258</v>
       </c>
@@ -11623,7 +11613,7 @@
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46259</v>
       </c>
@@ -11642,7 +11632,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46260</v>
       </c>
@@ -11661,7 +11651,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46261</v>
       </c>
@@ -11680,7 +11670,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46262</v>
       </c>
@@ -11699,7 +11689,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="31">
         <v>46263</v>
       </c>
@@ -11718,7 +11708,7 @@
       <c r="I37" s="35"/>
       <c r="J37" s="35"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>46264</v>
       </c>
@@ -11737,7 +11727,7 @@
       <c r="I38" s="35"/>
       <c r="J38" s="35"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>46265</v>
       </c>
@@ -11756,7 +11746,7 @@
       <c r="I39" s="30"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="46"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -11767,7 +11757,7 @@
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -11780,7 +11770,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="9"/>
@@ -11793,7 +11783,7 @@
       </c>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="122" t="s">
         <v>55</v>
       </c>
@@ -11804,7 +11794,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9">
+    <row r="44" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -11818,7 +11808,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="123" t="s">
         <v>57</v>
       </c>
@@ -11834,7 +11824,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1">
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -11848,7 +11838,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -11857,7 +11847,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -11868,7 +11858,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1">
+    <row r="49" spans="5:8" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -11879,56 +11869,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7">
-    <cfRule type="containsText" dxfId="38" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="31" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="30" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="29" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="27" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="26" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B49">
-    <cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="24" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E41 D43:E45 E48">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D40)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11980,18 +11970,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1366D5-46F5-410C-BC9F-D56DCF566D28}">
   <dimension ref="A5:J48"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" customWidth="1"/>
     <col min="4" max="5" width="20" style="23" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="23.09765625" style="23" customWidth="1"/>
     <col min="7" max="7" width="34" style="23" customWidth="1"/>
-    <col min="8" max="16384" width="8.75" style="23"/>
+    <col min="8" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -12001,7 +11991,7 @@
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
@@ -12015,10 +12005,10 @@
       <c r="H6" s="40"/>
       <c r="J6" s="41"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H7" s="40"/>
     </row>
-    <row r="8" spans="1:10" ht="25.15">
+    <row r="8" spans="1:10" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>3</v>
       </c>
@@ -12050,7 +12040,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46266</v>
       </c>
@@ -12083,7 +12073,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46267</v>
       </c>
@@ -12102,7 +12092,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46268</v>
       </c>
@@ -12121,7 +12111,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46269</v>
       </c>
@@ -12140,7 +12130,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
         <v>46270</v>
       </c>
@@ -12159,7 +12149,7 @@
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>46271</v>
       </c>
@@ -12178,7 +12168,7 @@
       <c r="I14" s="35"/>
       <c r="J14" s="35"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="22">
         <v>46272</v>
       </c>
@@ -12197,7 +12187,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="22">
         <v>46273</v>
       </c>
@@ -12216,7 +12206,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="22">
         <v>46274</v>
       </c>
@@ -12235,7 +12225,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="22">
         <v>46275</v>
       </c>
@@ -12254,7 +12244,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="22">
         <v>46276</v>
       </c>
@@ -12273,7 +12263,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
         <v>46277</v>
       </c>
@@ -12292,7 +12282,7 @@
       <c r="I20" s="35"/>
       <c r="J20" s="35"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
         <v>46278</v>
       </c>
@@ -12311,7 +12301,7 @@
       <c r="I21" s="35"/>
       <c r="J21" s="35"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46279</v>
       </c>
@@ -12330,7 +12320,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46280</v>
       </c>
@@ -12349,7 +12339,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46281</v>
       </c>
@@ -12368,7 +12358,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46282</v>
       </c>
@@ -12387,7 +12377,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46283</v>
       </c>
@@ -12406,7 +12396,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>46284</v>
       </c>
@@ -12425,7 +12415,7 @@
       <c r="I27" s="35"/>
       <c r="J27" s="35"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>46285</v>
       </c>
@@ -12444,7 +12434,7 @@
       <c r="I28" s="35"/>
       <c r="J28" s="35"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46286</v>
       </c>
@@ -12463,7 +12453,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46287</v>
       </c>
@@ -12482,7 +12472,7 @@
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="22">
         <v>46288</v>
       </c>
@@ -12501,7 +12491,7 @@
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="47">
         <v>46289</v>
       </c>
@@ -12532,7 +12522,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46290</v>
       </c>
@@ -12551,7 +12541,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="31">
         <v>46291</v>
       </c>
@@ -12570,7 +12560,7 @@
       <c r="I34" s="35"/>
       <c r="J34" s="35"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="31">
         <v>46292</v>
       </c>
@@ -12589,7 +12579,7 @@
       <c r="I35" s="35"/>
       <c r="J35" s="35"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46293</v>
       </c>
@@ -12608,7 +12598,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46294</v>
       </c>
@@ -12627,7 +12617,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46295</v>
       </c>
@@ -12646,7 +12636,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="39" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="46"/>
       <c r="B39" s="46"/>
       <c r="C39" s="45"/>
@@ -12657,7 +12647,7 @@
       <c r="H39" s="36"/>
       <c r="I39" s="37"/>
     </row>
-    <row r="40" spans="1:10" ht="13.9" customHeight="1">
+    <row r="40" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -12670,7 +12660,7 @@
       </c>
       <c r="H40" s="40"/>
     </row>
-    <row r="41" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="41" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="9"/>
@@ -12683,7 +12673,7 @@
       </c>
       <c r="H41" s="40"/>
     </row>
-    <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:10" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="122" t="s">
         <v>55</v>
       </c>
@@ -12694,7 +12684,7 @@
       <c r="F42" s="2"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:10" ht="13.9">
+    <row r="43" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="6"/>
@@ -12708,7 +12698,7 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="123" t="s">
         <v>57</v>
       </c>
@@ -12724,7 +12714,7 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.45" thickBot="1">
+    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -12738,7 +12728,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.9" thickBot="1">
+    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -12747,7 +12737,7 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -12758,7 +12748,7 @@
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.15" thickBot="1">
+    <row r="48" spans="1:10" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -12769,56 +12759,56 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D6:E7 D39:E40">
-    <cfRule type="containsText" dxfId="22" priority="14" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",A6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B48">
-    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Saturday">
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="Sunday">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Sunday">
       <formula>NOT(ISERROR(SEARCH("Sunday",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42:E44 E47">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="Religious Leave">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Religious Leave">
       <formula>NOT(ISERROR(SEARCH("Religious Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Birthday Leave">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Birthday Leave">
       <formula>NOT(ISERROR(SEARCH("Birthday Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Study Leave">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Study Leave">
       <formula>NOT(ISERROR(SEARCH("Study Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Family Responsibility Leave">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Family Responsibility Leave">
       <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Sick Leave">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Sick Leave">
       <formula>NOT(ISERROR(SEARCH("Sick Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Annual Leave">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Annual Leave">
       <formula>NOT(ISERROR(SEARCH("Annual Leave",D42)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12886,18 +12876,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368E8809-782A-4EC8-A7EE-23E6EB29126F}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.75" style="23"/>
-    <col min="5" max="5" width="13.25" style="23" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" style="23"/>
+    <col min="5" max="5" width="13.19921875" style="23" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="23" customWidth="1"/>
-    <col min="7" max="16384" width="8.75" style="23"/>
+    <col min="7" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13.5" customHeight="1">
+    <row r="1" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="80"/>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -12905,7 +12895,7 @@
       <c r="E1" s="80"/>
       <c r="F1" s="80"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
       <c r="C2" s="84"/>
@@ -12913,7 +12903,7 @@
       <c r="E2" s="84"/>
       <c r="F2" s="84"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="79"/>
       <c r="B3" s="79"/>
       <c r="C3" s="85"/>
@@ -12921,7 +12911,7 @@
       <c r="E3" s="85"/>
       <c r="F3" s="85"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="79"/>
       <c r="B4" s="79"/>
       <c r="C4" s="86"/>
@@ -12929,7 +12919,7 @@
       <c r="E4" s="86"/>
       <c r="F4" s="86"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -12941,7 +12931,7 @@
       <c r="E5" s="86"/>
       <c r="F5" s="86"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="79" t="s">
         <v>70</v>
       </c>
@@ -12954,7 +12944,7 @@
       <c r="E6" s="85"/>
       <c r="F6" s="85"/>
     </row>
-    <row r="7" spans="1:15" ht="13.5" customHeight="1">
+    <row r="7" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="73"/>
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
@@ -12962,139 +12952,139 @@
       <c r="E7" s="85"/>
       <c r="F7" s="85"/>
     </row>
-    <row r="8" spans="1:15" ht="27.4" customHeight="1">
-      <c r="A8" s="132" t="s">
+    <row r="8" spans="1:15" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="129" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-    </row>
-    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B8" s="129"/>
+      <c r="C8" s="129"/>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+    </row>
+    <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="135" t="s">
+      <c r="B9" s="126" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="136"/>
-      <c r="D9" s="135" t="s">
+      <c r="C9" s="127"/>
+      <c r="D9" s="126" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="136"/>
+      <c r="E9" s="127"/>
       <c r="F9" s="83" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="126" t="s">
+      <c r="B10" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="126"/>
-      <c r="D10" s="126" t="s">
+      <c r="C10" s="128"/>
+      <c r="D10" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="126"/>
+      <c r="E10" s="128"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="133" t="s">
+      <c r="G10" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="134"/>
-      <c r="N10" s="134"/>
-      <c r="O10" s="134"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="125"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="125"/>
+      <c r="O10" s="125"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="124" t="s">
+      <c r="B11" s="130" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="125"/>
-      <c r="D11" s="126" t="s">
+      <c r="C11" s="131"/>
+      <c r="D11" s="128" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="126"/>
+      <c r="E11" s="128"/>
       <c r="F11" s="77"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="124" t="s">
+      <c r="B12" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="128"/>
       <c r="F12" s="77"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="124"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
+      <c r="B13" s="130"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="128"/>
       <c r="F13" s="77"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="124"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
       <c r="F14" s="77"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="130"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
+      <c r="B15" s="135"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="128"/>
       <c r="F15" s="77"/>
     </row>
-    <row r="16" spans="1:15" ht="13.15" thickBot="1">
+    <row r="16" spans="1:15" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="124"/>
-      <c r="C16" s="125"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="131"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
       <c r="F16" s="77"/>
     </row>
-    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A17" s="127" t="s">
+    <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="132" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="129"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="134"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="73"/>
       <c r="B18" s="74"/>
       <c r="C18" s="74"/>
@@ -13104,16 +13094,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -13123,6 +13103,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -13152,19 +13142,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0517D5F3-AC91-43ED-96BB-0299CBED5EE0}">
   <dimension ref="A4:F23"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="23" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="23" customWidth="1"/>
-    <col min="4" max="16384" width="8.75" style="23"/>
+    <col min="2" max="2" width="11.69921875" style="23" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" style="23" customWidth="1"/>
+    <col min="4" max="16384" width="8.69921875" style="23"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="137"/>
       <c r="B4" s="137"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>0</v>
       </c>
@@ -13172,23 +13162,23 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="79" t="s">
         <v>83</v>
       </c>
       <c r="B6" s="79"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="95" t="s">
         <v>84</v>
       </c>
       <c r="B7" s="95"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="96"/>
       <c r="B8" s="85"/>
     </row>
-    <row r="9" spans="1:6" ht="27.4" customHeight="1">
+    <row r="9" spans="1:6" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="150" t="s">
         <v>85</v>
       </c>
@@ -13198,7 +13188,7 @@
       <c r="E9" s="150"/>
       <c r="F9" s="150"/>
     </row>
-    <row r="10" spans="1:6" ht="25.15">
+    <row r="10" spans="1:6" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A10" s="87" t="s">
         <v>86</v>
       </c>
@@ -13218,7 +13208,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="87" t="s">
         <v>92</v>
       </c>
@@ -13230,7 +13220,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="87"/>
       <c r="B12" s="87"/>
       <c r="C12" s="87"/>
@@ -13238,7 +13228,7 @@
       <c r="E12" s="87"/>
       <c r="F12" s="87"/>
     </row>
-    <row r="13" spans="1:6" ht="13.15" thickBot="1">
+    <row r="13" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="87"/>
       <c r="B13" s="87"/>
       <c r="C13" s="87"/>
@@ -13246,7 +13236,7 @@
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
     </row>
-    <row r="14" spans="1:6" ht="13.15" thickBot="1">
+    <row r="14" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="88"/>
       <c r="B14" s="89"/>
       <c r="C14" s="89"/>
@@ -13257,7 +13247,7 @@
       <c r="E14" s="89"/>
       <c r="F14" s="91"/>
     </row>
-    <row r="15" spans="1:6" ht="13.15" thickBot="1">
+    <row r="15" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="141"/>
       <c r="B15" s="142"/>
       <c r="C15" s="142"/>
@@ -13265,7 +13255,7 @@
       <c r="E15" s="142"/>
       <c r="F15" s="142"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="151" t="s">
         <v>94</v>
       </c>
@@ -13275,7 +13265,7 @@
       <c r="E16" s="152"/>
       <c r="F16" s="153"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="138"/>
       <c r="B17" s="139"/>
       <c r="C17" s="139"/>
@@ -13283,7 +13273,7 @@
       <c r="E17" s="139"/>
       <c r="F17" s="140"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="138"/>
       <c r="B18" s="139"/>
       <c r="C18" s="139"/>
@@ -13291,7 +13281,7 @@
       <c r="E18" s="139"/>
       <c r="F18" s="140"/>
     </row>
-    <row r="19" spans="1:6" ht="13.15" thickBot="1">
+    <row r="19" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="141"/>
       <c r="B19" s="142"/>
       <c r="C19" s="142"/>
@@ -13299,8 +13289,8 @@
       <c r="E19" s="142"/>
       <c r="F19" s="143"/>
     </row>
-    <row r="20" spans="1:6" ht="13.15" thickBot="1"/>
-    <row r="21" spans="1:6">
+    <row r="20" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="92" t="s">
         <v>3</v>
       </c>
@@ -13310,7 +13300,7 @@
       <c r="E21" s="144"/>
       <c r="F21" s="145"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="93" t="s">
         <v>95</v>
       </c>
@@ -13320,7 +13310,7 @@
       <c r="E22" s="146"/>
       <c r="F22" s="147"/>
     </row>
-    <row r="23" spans="1:6" ht="13.15" thickBot="1">
+    <row r="23" spans="1:6" ht="13.2" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="94" t="s">
         <v>96</v>
       </c>
@@ -13384,18 +13374,18 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="B2:J76"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="52"/>
+    <col min="1" max="1" width="8.69921875" style="52"/>
     <col min="2" max="2" width="25.5" style="52" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="52"/>
-    <col min="4" max="4" width="19.25" style="52" customWidth="1"/>
-    <col min="5" max="5" width="8.75" style="52"/>
-    <col min="6" max="6" width="21.75" style="52" customWidth="1"/>
-    <col min="7" max="16384" width="8.75" style="52"/>
+    <col min="3" max="3" width="8.69921875" style="52"/>
+    <col min="4" max="4" width="19.19921875" style="52" customWidth="1"/>
+    <col min="5" max="5" width="8.69921875" style="52"/>
+    <col min="6" max="6" width="21.69921875" style="52" customWidth="1"/>
+    <col min="7" max="16384" width="8.69921875" style="52"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1">
+    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="66" t="s">
         <v>14</v>
       </c>
@@ -13412,7 +13402,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="66" t="s">
         <v>99</v>
       </c>
@@ -13430,7 +13420,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="66" t="s">
         <v>102</v>
       </c>
@@ -13448,7 +13438,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="66" t="s">
         <v>105</v>
       </c>
@@ -13463,7 +13453,7 @@
       </c>
       <c r="I5" s="100"/>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="66" t="s">
         <v>109</v>
       </c>
@@ -13478,7 +13468,7 @@
       </c>
       <c r="I6" s="101"/>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="66" t="s">
         <v>113</v>
       </c>
@@ -13493,7 +13483,7 @@
       </c>
       <c r="I7" s="102"/>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="66" t="s">
         <v>116</v>
       </c>
@@ -13511,7 +13501,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="66" t="s">
         <v>120</v>
       </c>
@@ -13529,7 +13519,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="66" t="s">
         <v>124</v>
       </c>
@@ -13544,7 +13534,7 @@
       </c>
       <c r="I10" s="102"/>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="66" t="s">
         <v>128</v>
       </c>
@@ -13562,7 +13552,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="66" t="s">
         <v>133</v>
       </c>
@@ -13577,7 +13567,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="66" t="s">
         <v>137</v>
       </c>
@@ -13589,7 +13579,7 @@
       </c>
       <c r="I13" s="103"/>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="66" t="s">
         <v>139</v>
       </c>
@@ -13602,7 +13592,7 @@
       </c>
       <c r="I14" s="104"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="66" t="s">
         <v>141</v>
       </c>
@@ -13615,7 +13605,7 @@
       </c>
       <c r="I15" s="103"/>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="66" t="s">
         <v>143</v>
       </c>
@@ -13628,7 +13618,7 @@
       </c>
       <c r="I16" s="105"/>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="66" t="s">
         <v>145</v>
       </c>
@@ -13641,7 +13631,7 @@
       </c>
       <c r="I17" s="103"/>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="66" t="s">
         <v>148</v>
       </c>
@@ -13654,7 +13644,7 @@
       </c>
       <c r="I18" s="105"/>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="66" t="s">
         <v>151</v>
       </c>
@@ -13667,7 +13657,7 @@
       </c>
       <c r="I19" s="106"/>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="66" t="s">
         <v>153</v>
       </c>
@@ -13680,7 +13670,7 @@
       </c>
       <c r="I20" s="104"/>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="66" t="s">
         <v>156</v>
       </c>
@@ -13693,7 +13683,7 @@
       </c>
       <c r="I21" s="102"/>
     </row>
-    <row r="22" spans="2:9" ht="27.6">
+    <row r="22" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B22" s="66" t="s">
         <v>159</v>
       </c>
@@ -13706,7 +13696,7 @@
       </c>
       <c r="I22" s="107"/>
     </row>
-    <row r="23" spans="2:9">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="66" t="s">
         <v>162</v>
       </c>
@@ -13719,7 +13709,7 @@
       </c>
       <c r="I23" s="108"/>
     </row>
-    <row r="24" spans="2:9">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="66" t="s">
         <v>164</v>
       </c>
@@ -13732,7 +13722,7 @@
       </c>
       <c r="I24" s="109"/>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="66" t="s">
         <v>166</v>
       </c>
@@ -13745,7 +13735,7 @@
       </c>
       <c r="I25" s="110"/>
     </row>
-    <row r="26" spans="2:9">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="66" t="s">
         <v>169</v>
       </c>
@@ -13756,7 +13746,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="27" spans="2:9">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="66" t="s">
         <v>172</v>
       </c>
@@ -13769,7 +13759,7 @@
       </c>
       <c r="I27" s="108"/>
     </row>
-    <row r="28" spans="2:9">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="66" t="s">
         <v>175</v>
       </c>
@@ -13782,7 +13772,7 @@
       </c>
       <c r="I28" s="70"/>
     </row>
-    <row r="29" spans="2:9">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="66" t="s">
         <v>178</v>
       </c>
@@ -13794,7 +13784,7 @@
       </c>
       <c r="I29" s="111"/>
     </row>
-    <row r="30" spans="2:9">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="66" t="s">
         <v>181</v>
       </c>
@@ -13806,7 +13796,7 @@
       </c>
       <c r="I30" s="109"/>
     </row>
-    <row r="31" spans="2:9">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="66" t="s">
         <v>184</v>
       </c>
@@ -13817,7 +13807,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="32" spans="2:9">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="66" t="s">
         <v>187</v>
       </c>
@@ -13829,7 +13819,7 @@
       </c>
       <c r="I32" s="110"/>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="66" t="s">
         <v>190</v>
       </c>
@@ -13841,7 +13831,7 @@
       </c>
       <c r="I33" s="110"/>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="66" t="s">
         <v>192</v>
       </c>
@@ -13853,7 +13843,7 @@
       </c>
       <c r="I34" s="69"/>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="66" t="s">
         <v>195</v>
       </c>
@@ -13865,7 +13855,7 @@
       </c>
       <c r="I35" s="109"/>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="66" t="s">
         <v>198</v>
       </c>
@@ -13877,7 +13867,7 @@
       </c>
       <c r="I36" s="102"/>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="66" t="s">
         <v>201</v>
       </c>
@@ -13889,7 +13879,7 @@
       </c>
       <c r="I37" s="110"/>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="66" t="s">
         <v>204</v>
       </c>
@@ -13901,7 +13891,7 @@
       </c>
       <c r="I38" s="109"/>
     </row>
-    <row r="39" spans="2:9" ht="27.6">
+    <row r="39" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B39" s="66" t="s">
         <v>205</v>
       </c>
@@ -13913,7 +13903,7 @@
       </c>
       <c r="I39" s="111"/>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="66" t="s">
         <v>208</v>
       </c>
@@ -13925,7 +13915,7 @@
       </c>
       <c r="I40" s="112"/>
     </row>
-    <row r="41" spans="2:9">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41" s="66" t="s">
         <v>211</v>
       </c>
@@ -13935,7 +13925,7 @@
       </c>
       <c r="I41" s="112"/>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42" s="66" t="s">
         <v>213</v>
       </c>
@@ -13944,7 +13934,7 @@
       </c>
       <c r="I42" s="109"/>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43" s="66" t="s">
         <v>215</v>
       </c>
@@ -13953,7 +13943,7 @@
       </c>
       <c r="I43" s="111"/>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="121" t="s">
         <v>217</v>
       </c>
@@ -13961,158 +13951,158 @@
         <v>218</v>
       </c>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H45" s="112" t="s">
         <v>219</v>
       </c>
       <c r="I45" s="110"/>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H46" s="70" t="s">
         <v>220</v>
       </c>
       <c r="I46" s="113"/>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="62"/>
       <c r="H47" s="112" t="s">
         <v>221</v>
       </c>
       <c r="I47" s="112"/>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H48" s="70" t="s">
         <v>222</v>
       </c>
       <c r="I48" s="112"/>
     </row>
-    <row r="49" spans="8:9">
+    <row r="49" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H49" s="109" t="s">
         <v>223</v>
       </c>
       <c r="I49" s="112"/>
     </row>
-    <row r="50" spans="8:9">
+    <row r="50" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H50" s="70" t="s">
         <v>224</v>
       </c>
       <c r="I50" s="112"/>
     </row>
-    <row r="51" spans="8:9">
+    <row r="51" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H51" s="69" t="s">
         <v>225</v>
       </c>
       <c r="I51" s="112"/>
     </row>
-    <row r="52" spans="8:9">
+    <row r="52" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H52" s="112" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="53" spans="8:9">
+    <row r="53" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H53" s="109" t="s">
         <v>227</v>
       </c>
       <c r="I53" s="112"/>
     </row>
-    <row r="54" spans="8:9">
+    <row r="54" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H54" s="69" t="s">
         <v>228</v>
       </c>
       <c r="I54" s="111"/>
     </row>
-    <row r="55" spans="8:9">
+    <row r="55" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H55" s="70" t="s">
         <v>229</v>
       </c>
       <c r="I55" s="111"/>
     </row>
-    <row r="56" spans="8:9">
+    <row r="56" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H56" s="109" t="s">
         <v>230</v>
       </c>
       <c r="I56" s="70"/>
     </row>
-    <row r="57" spans="8:9">
+    <row r="57" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H57" s="70" t="s">
         <v>231</v>
       </c>
       <c r="I57" s="112"/>
     </row>
-    <row r="58" spans="8:9">
+    <row r="58" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H58" s="70" t="s">
         <v>232</v>
       </c>
       <c r="I58" s="112"/>
     </row>
-    <row r="59" spans="8:9">
+    <row r="59" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H59" s="112" t="s">
         <v>233</v>
       </c>
       <c r="I59" s="115"/>
     </row>
-    <row r="60" spans="8:9">
+    <row r="60" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H60" s="115" t="s">
         <v>234</v>
       </c>
       <c r="I60" s="69"/>
     </row>
-    <row r="61" spans="8:9">
+    <row r="61" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H61" s="69" t="s">
         <v>235</v>
       </c>
       <c r="I61" s="110"/>
     </row>
-    <row r="62" spans="8:9">
+    <row r="62" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H62" s="69" t="s">
         <v>236</v>
       </c>
       <c r="I62" s="69"/>
     </row>
-    <row r="63" spans="8:9">
+    <row r="63" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H63" s="110" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="64" spans="8:9">
+    <row r="64" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H64" s="120" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="65" spans="8:8">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H65" s="111"/>
     </row>
-    <row r="66" spans="8:8">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H66" s="109"/>
     </row>
-    <row r="67" spans="8:8">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H67" s="112"/>
     </row>
-    <row r="68" spans="8:8">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H68" s="102"/>
     </row>
-    <row r="69" spans="8:8">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H69" s="112"/>
     </row>
-    <row r="70" spans="8:8">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H70" s="70"/>
     </row>
-    <row r="71" spans="8:8">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H71" s="109"/>
     </row>
-    <row r="72" spans="8:8">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H72" s="111"/>
     </row>
-    <row r="73" spans="8:8">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H73" s="100"/>
     </row>
-    <row r="74" spans="8:8">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H74" s="107"/>
     </row>
-    <row r="75" spans="8:8">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H75" s="116"/>
     </row>
-    <row r="76" spans="8:8">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H76" s="116"/>
     </row>
   </sheetData>
@@ -14131,12 +14121,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14278,21 +14265,47 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924AA10C-4249-48F1-8B83-8614A59DE81A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7322752-B369-4656-AA67-53439EDC6B25}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B260CF4F-4CB2-4BF2-AFC7-CD16C463662A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B260CF4F-4CB2-4BF2-AFC7-CD16C463662A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7322752-B369-4656-AA67-53439EDC6B25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924AA10C-4249-48F1-8B83-8614A59DE81A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Timesheet-Project/Timesheet 3/Lwazisile/Lwazisile_Mhlambi_April_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Lwazisile/Lwazisile_Mhlambi_April_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Lwazisile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE14221B-A312-4EAE-8F76-E53953F77108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B834CAE-4440-4A6C-AB0A-F854A5797BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3204" yWindow="3204" windowWidth="17280" windowHeight="8880" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
